--- a/important_mails_2026-05-24.xlsx
+++ b/important_mails_2026-05-24.xlsx
@@ -1104,7 +1104,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1119,125 +1119,21 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 08:49:45 +0000</t>
+          <t>Tue, 19 May 2026 17:11:27 +0000</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Your payment is on the way</t>
+          <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement attempted
-Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
-On 05/17/26 08:49 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
- 210.40.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon Store,
-Amazon Services
-Help us improve your payment experience on Amaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 17 May 2026 08:47:51 +0000</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement Attempted
-Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
-On 05/17/26 08:47 BST, we initiated a transfer to your payment method (bank account ending in 191) in the amount of £
- 329.80.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To find out more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon store,
-Amazon Services
-Help us improve your payment experience on Ama</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 19 May 2026 17:11:27 +0000</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.com Inventory - Action Required</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -1256,40 +1152,40 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:24:17 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1305,40 +1201,40 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:03:38 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1352,40 +1248,40 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:02:28 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1399,85 +1295,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 17 May 2026 14:07:57 +0000</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
- MARKETPLACE: 1 - PS - APPEAL</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Hello,
-We have reviewed your appeal request. We are rejecting your appeal because the detail page has an image of a child playing with the product. We request you take the following action:
-Please remove the image from the detail page. This requirement helps ensure products are compliant with local laws and safe for customers.
-For more information on compliance requirements for Arts &amp; Crafts, please visit: https://sellercentral.amazon.com/help/hub/reference/external/GKJRA3FRPRKVBJJS
-Once testing or verification is requested, please work with the chosen source to provide all requested information to complete testing of your product or verification of your existing test documents. Once the third-party TIC services provide Amazon with test or verification results confirming compliance with Amazon's policies, your product will be eligible for sale in US store. No further action will be required.
-Without completing the steps mentioned above, we will not be able to proceed with your appeal/reinstatement.
-We appreciate your cooperation on this important matter.
-Note: This email was sent from a no-reply mailbox. Please don't reply to this email. Kindly navigate via Account Health Dashboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 17:10:56 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -1493,39 +1343,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 08:56:06 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>5月27日前入库助力Prime Day成功</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -1555,39 +1405,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 14:06:09 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Seller News: May 2026</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1602,39 +1452,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 13:00:10 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Seller News: May 2026</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1649,39 +1499,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 10:15:46 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -1696,39 +1546,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 15:00:47 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1743,39 +1593,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 13:54:37 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -1790,39 +1640,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 17:10:53 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -1840,39 +1690,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:55:42 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Ship Smarter: Get 3 FREE Brokerage Fees: Limited Time C2S2 Offer 🚀</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z3hy11/6664114770/h/cIM7P1R6ABFsNRmzeIU2ASpTCxzOevVrUjDi2lts12A)
 Ship Cross-Border &amp; Save Big. Get Started with C2S2 Today.
@@ -1889,39 +1739,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 06:33:16 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1940,86 +1790,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 17 May 2026 08:48:46 +0000</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Pagamento elaborato con successo</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-This title will display on mobile devices
- Congratulazioni. Il pagamento è stato elaborato con successo e ti sarà accreditato a breve.
- Tentativo di pagamento
-Congratulazioni Weihai EU! Il pagamento è stato elaborato con successo e ti sarà accreditato nel giro di da tre a cinque giorni.
-In data 05/17/26 08:48 CEST, abbiamo avviato un trasferimento sul tuo metodo di pagamento (conto bancario che termina con 229) dell’importo di €
- 386,80.
- Se l’importo è inferiore a quanto atteso, tieni in considerazione le seguenti domande:
- Hai un saldo non disponibile? Amazon potrebbe trattenere una certa somma per coprire i costi di eventuali resi, reclami o contestazioni di una transazione (chargeback) da parte degli acquirenti. In questo caso, il saldo finale nel tuo report sui pagamenti mostrerà il saldo non disponibile corrispondente alla cifra trattenuta.
- Le tue vendite coprono tutte le commissioni e i resi per questo ciclo di fatturazione? L’importo del pagamento rispecchia le attività di vendita, le commissioni di vendita e le tariffe per promozioni o servizi. Ti consigliamo di rivedere il report sui pagamenti nella scheda Report di Seller Central per comprendere le diverse spese che </t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sat, 23 May 2026 04:06:08 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-04</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2042,39 +1845,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Sat, 23 May 2026 03:17:21 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2098,40 +1901,40 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 07:25:40 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Update VAT registration information to reinstate Inventory and FBA
  functionality of your Amazon.it store</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -2147,39 +1950,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 02:39:33 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (ZazNpo+O9J)</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2205,39 +2008,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 02:56:06 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2253,39 +2056,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:45:41 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq4e6nl040)</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2310,39 +2113,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 05:42:00 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (zl4CmeMn1C)</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2362,39 +2165,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 18:10:42 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (toabAY9R4I)</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2414,39 +2217,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 11:59:35 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cp3IU6ppnV)</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2466,39 +2269,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 16:07:01 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2519,39 +2322,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 13:03:07 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (2604121A02)</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2571,39 +2374,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Mon, 4 May 2026 16:59:42 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (AOOD6vlnxr)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2623,39 +2426,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:32:02 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $69.79 in an attempt to settle your Amazon seller account balance.
@@ -2671,39 +2474,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 07:28:26 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (5NT+O11io4)</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2723,39 +2526,143 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 17 May 2026 08:49:45 +0000</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement attempted
+Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
+On 05/17/26 08:49 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
+ 210.40.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon Store,
+Amazon Services
+Help us improve your payment experience on Amaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 17 May 2026 08:47:51 +0000</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
+On 05/17/26 08:47 BST, we initiated a transfer to your payment method (bank account ending in 191) in the amount of £
+ 329.80.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To find out more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+Help us improve your payment experience on Ama</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:36:52 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2775,39 +2682,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:51:22 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -2823,39 +2730,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:50:04 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2872,39 +2779,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:49:55 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2924,39 +2831,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:53:51 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -2973,39 +2880,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:42 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3022,39 +2929,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:28 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3074,39 +2981,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3126,39 +3033,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 03:44:19 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3175,39 +3082,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 15:00:39 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 87.72 in an attempt to settle your account balance.
@@ -3222,39 +3129,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:45:41 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3270,39 +3177,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:23:38 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>跨账户负余额调整</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3322,39 +3229,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3374,39 +3281,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:27:01 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3423,39 +3330,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:26:48 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3475,39 +3382,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3527,39 +3434,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:56 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3576,39 +3483,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:50 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3628,39 +3535,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 05:12:21 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;seller-notification@amazon.ie&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Outstanding balance on your Amazon account</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Hello,
  You have an outstanding balance on your account in the amount of 7,79 EUR. We will debit this amount from the credit card (Visa) that you registered as the charge method for your account.
@@ -3674,39 +3581,85 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 17 May 2026 14:07:57 +0000</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
+ MARKETPLACE: 1 - PS - APPEAL</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+We have reviewed your appeal request. We are rejecting your appeal because the detail page has an image of a child playing with the product. We request you take the following action:
+Please remove the image from the detail page. This requirement helps ensure products are compliant with local laws and safe for customers.
+For more information on compliance requirements for Arts &amp; Crafts, please visit: https://sellercentral.amazon.com/help/hub/reference/external/GKJRA3FRPRKVBJJS
+Once testing or verification is requested, please work with the chosen source to provide all requested information to complete testing of your product or verification of your existing test documents. Once the third-party TIC services provide Amazon with test or verification results confirming compliance with Amazon's policies, your product will be eligible for sale in US store. No further action will be required.
+Without completing the steps mentioned above, we will not be able to proceed with your appeal/reinstatement.
+We appreciate your cooperation on this important matter.
+Note: This email was sent from a no-reply mailbox. Please don't reply to this email. Kindly navigate via Account Health Dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 03:03:13 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -3726,39 +3679,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 07:42:16 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-de@amazon.com" &lt;fba-3p-buyability-improvement-de@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -3783,39 +3736,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 10:44:21 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-it@amazon.com" &lt;fba-3p-buyability-improvement-it@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -3840,40 +3793,40 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:51 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3888,40 +3841,40 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:28 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3935,40 +3888,40 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:15:37 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3982,41 +3935,41 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:37:14 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour
  les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
  for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
@@ -4027,39 +3980,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 17:50:39 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4078,39 +4031,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 12:49:24 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4134,39 +4087,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 02:13:07 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4184,39 +4137,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 13:18:47 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4234,39 +4187,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 13:15:01 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4284,39 +4237,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:13:49 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4334,39 +4287,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:19:29 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4384,39 +4337,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 12:52:07 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -4432,39 +4385,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:11:27 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4482,39 +4435,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:14:16 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4532,39 +4485,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 13:03:36 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -4574,39 +4527,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 09:05:17 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>【请勿回复此日志，如有问题请加入下方邮件中的企微群】
 卖家您好，
@@ -4627,39 +4580,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:13:11 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4675,39 +4628,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:52:19 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4726,39 +4679,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 03:13:33 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20093870001] Other account issues</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Hello from Amazon Selling Partner Support,
 My name is Ritam. I am a Live Channel Specialist and I'm contacting you to follow up on your concern regarding the reinstatement of your listing B0FCDRNTT8.
@@ -4769,39 +4722,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 17:15:23 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4820,39 +4773,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:37 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -4871,39 +4824,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:18 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -4919,6 +4872,53 @@
  If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
  For step-by-step instructions, see our Submit compliance documents or appeal a documentation request help page.
  To avoid further impact on your account, close or delete any non-compliant listings that you</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 17 May 2026 08:48:46 +0000</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Pagamento elaborato con successo</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+This title will display on mobile devices
+ Congratulazioni. Il pagamento è stato elaborato con successo e ti sarà accreditato a breve.
+ Tentativo di pagamento
+Congratulazioni Weihai EU! Il pagamento è stato elaborato con successo e ti sarà accreditato nel giro di da tre a cinque giorni.
+In data 05/17/26 08:48 CEST, abbiamo avviato un trasferimento sul tuo metodo di pagamento (conto bancario che termina con 229) dell’importo di €
+ 386,80.
+ Se l’importo è inferiore a quanto atteso, tieni in considerazione le seguenti domande:
+ Hai un saldo non disponibile? Amazon potrebbe trattenere una certa somma per coprire i costi di eventuali resi, reclami o contestazioni di una transazione (chargeback) da parte degli acquirenti. In questo caso, il saldo finale nel tuo report sui pagamenti mostrerà il saldo non disponibile corrispondente alla cifra trattenuta.
+ Le tue vendite coprono tutte le commissioni e i resi per questo ciclo di fatturazione? L’importo del pagamento rispecchia le attività di vendita, le commissioni di vendita e le tariffe per promozioni o servizi. Ti consigliamo di rivedere il report sui pagamenti nella scheda Report di Seller Central per comprendere le diverse spese che </t>
         </is>
       </c>
     </row>

--- a/important_mails_2026-05-24.xlsx
+++ b/important_mails_2026-05-24.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H180"/>
+  <dimension ref="A1:H171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -552,69 +552,21 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 14:33:15 +0000</t>
+          <t>Fri, 22 May 2026 15:30:35 +0000</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Balance paid on your Amazon seller account</t>
+          <t>Your payment is on the way</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon Services.
- We have charged your credit card for $105.47 in an attempt to settle your Amazon seller account balance.
- Note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. If that is the case, we will continue to charge your credit card as often as every 24 hours until the remaining balance in your Amazon seller account is paid in full.
- You can also use the Make a Payment feature to repay the balance you owe. For more information, see Making a Payment .
- You can view your payment activity at any time by logging in to your seller account and going to your Payments Report .
- Thank you for selling on Amazon.
- Amazon Services
- Help us improve your experience on selling on Amazon through this brief survey:
- https://amazonexteu.qualtrics.com/jfe/form/SV_eUKdboEQhg1YpuK?cID=10038096056-202605171349
- Was this email helpful?
- SPC-USAmazon-211108450578443</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 22 May 2026 15:30:35 +0000</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -634,39 +586,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 15:29:45 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -683,39 +635,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 14:22:00 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -735,39 +687,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 13:54:11 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -787,39 +739,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:21:19 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January - March 2026</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -836,39 +788,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:07:05 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January-March 2026</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -885,39 +837,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 14:48:57 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -937,39 +889,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:42 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -993,39 +945,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:19 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -1049,39 +1001,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 13:46:45 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1101,39 +1053,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 17:11:27 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -1152,40 +1104,40 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:24:17 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1201,40 +1153,40 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:03:38 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1248,40 +1200,40 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:02:28 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1295,39 +1247,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 17:10:56 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -1343,39 +1295,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 08:56:06 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>5月27日前入库助力Prime Day成功</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -1405,39 +1357,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 14:06:09 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Seller News: May 2026</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1452,39 +1404,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 13:00:10 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Seller News: May 2026</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1499,39 +1451,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 10:15:46 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -1546,39 +1498,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 15:00:47 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1593,39 +1545,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 13:54:37 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -1640,39 +1592,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 17:10:53 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -1690,39 +1642,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:55:42 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Ship Smarter: Get 3 FREE Brokerage Fees: Limited Time C2S2 Offer 🚀</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z3hy11/6664114770/h/cIM7P1R6ABFsNRmzeIU2ASpTCxzOevVrUjDi2lts12A)
 Ship Cross-Border &amp; Save Big. Get Started with C2S2 Today.
@@ -1739,39 +1691,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 06:33:16 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1790,39 +1742,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Sat, 23 May 2026 04:06:08 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-04</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1845,39 +1797,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sat, 23 May 2026 03:17:21 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1901,40 +1853,40 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 07:25:40 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Update VAT registration information to reinstate Inventory and FBA
  functionality of your Amazon.it store</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1947,6 +1899,54 @@
  To learn more visit our
  European VAT registration requirements help page.
  How do I restore invent</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 17 May 2026 14:33:15 +0000</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Balance paid on your Amazon seller account</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon Services.
+ We have charged your credit card for $105.47 in an attempt to settle your Amazon seller account balance.
+ Note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. If that is the case, we will continue to charge your credit card as often as every 24 hours until the remaining balance in your Amazon seller account is paid in full.
+ You can also use the Make a Payment feature to repay the balance you owe. For more information, see Making a Payment .
+ You can view your payment activity at any time by logging in to your seller account and going to your Payments Report .
+ Thank you for selling on Amazon.
+ Amazon Services
+ Help us improve your experience on selling on Amazon through this brief survey:
+ https://amazonexteu.qualtrics.com/jfe/form/SV_eUKdboEQhg1YpuK?cID=10038096056-202605171349
+ Was this email helpful?
+ SPC-USAmazon-211108450578443</t>
         </is>
       </c>
     </row>
@@ -3538,7 +3538,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3553,68 +3553,22 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 05:12:21 +0000</t>
+          <t>Sun, 17 May 2026 14:07:57 +0000</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Amazon Payments Europe &lt;seller-notification@amazon.ie&gt;</t>
+          <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Outstanding balance on your Amazon account</t>
+          <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
+ MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>Hello,
- You have an outstanding balance on your account in the amount of 7,79 EUR. We will debit this amount from the credit card (Visa) that you registered as the charge method for your account.
- If this card has a credit limit, we may continue to charge this card until the outstanding balance is fully paid.
- For further information, search for “Make a Payment” in Seller Central Help (https://sellercentral-europe.amazon.com/gp/help/201058620).
- To learn more about your payment reports and activity, search for “View My Payments Reports” in Seller Central Help (https://sellercentral-europe.amazon.com/gp/help/60511).
- Sincerely,
- Amazon Payments Europe SCA (société en commandite par actions), partnership limited by shares, is a company registered in Luxembourg, Registration Number (RCS Luxembourg) B 153 265, with its corporate office at 38 avenue John F. Kennedy, L-1855 Luxembourg. VAT Number LU 24448288. Amazon Payments Europe SCA is authorised by the Commission de Surveillance du Secteur Financier as an Electronic Money Issuer (licence number 36/10).
- 此电子邮件是否有用？
- SPC-EUAmazon-1724035881032491</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 17 May 2026 14:07:57 +0000</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
- MARKETPLACE: 1 - PS - APPEAL</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Hello,
 We have reviewed your appeal request. We are rejecting your appeal because the detail page has an image of a child playing with the product. We request you take the following action:
@@ -3627,39 +3581,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 03:03:13 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -3679,39 +3633,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 07:42:16 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-de@amazon.com" &lt;fba-3p-buyability-improvement-de@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -3736,39 +3690,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 10:44:21 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-it@amazon.com" &lt;fba-3p-buyability-improvement-it@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -3793,40 +3747,40 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:51 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3841,40 +3795,40 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:28 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3888,40 +3842,40 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:15:37 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3935,41 +3889,41 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:37:14 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour
  les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
  for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
@@ -3980,39 +3934,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 17:50:39 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4031,39 +3985,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 12:49:24 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4087,39 +4041,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 02:13:07 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4137,39 +4091,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 13:18:47 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4187,39 +4141,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 13:15:01 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4237,39 +4191,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:13:49 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4287,39 +4241,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:19:29 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4337,39 +4291,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 12:52:07 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -4385,39 +4339,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:11:27 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4435,39 +4389,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:14:16 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4485,39 +4439,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 13:03:36 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -4527,39 +4481,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 09:05:17 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>【请勿回复此日志，如有问题请加入下方邮件中的企微群】
 卖家您好，
@@ -4580,39 +4534,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:13:11 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4628,39 +4582,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:52:19 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4679,39 +4633,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 03:13:33 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20093870001] Other account issues</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Hello from Amazon Selling Partner Support,
 My name is Ritam. I am a Live Channel Specialist and I'm contacting you to follow up on your concern regarding the reinstatement of your listing B0FCDRNTT8.
@@ -4722,39 +4676,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 17:15:23 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4773,141 +4727,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 19:15:37 +0000</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 17 May 2026 08:48:46 +0000</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to avoid listing deactivation</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai EU,
- Some of your listings are at risk of deactivation due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
- For step-by-step instructions, see our Submit compliance documents or appeal a documentation request help page.
- To avoid further impact to your account, close or delete any non-compliant listings that you do</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 19:09:18 +0000</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to avoid listing deactivation</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai EU,
- Some of your listings are at risk of deactivation due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listing?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents.
--
- If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
- For step-by-step instructions, see our Submit compliance documents or appeal a documentation request help page.
- To avoid further impact on your account, close or delete any non-compliant listings that you</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 17 May 2026 08:48:46 +0000</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -4922,40 +4774,40 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 05:21:00 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4971,39 +4823,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 17:10:29 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -5019,39 +4871,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:52:25 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;store-news@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>EchoPlan Magnetic Blocks is still in your cart</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Still thinking about it? https://www.amazon.com/gp/cart/view.html?ref_=cor
 EchoPlan 200PCS Magnetic Blocks, Magnetic Building Blocks, Magnet Blocks Cubes, STEM Educational Stacking Magnet Toy for Kids Ages 3 4 5 6 7 8 9 10 11, Birthday Gifts for Boys and Girls, 1&amp;quot; Large Size
@@ -5072,39 +4924,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:07:42 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5119,39 +4971,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 03:00:00 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -5181,39 +5033,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 16:40:18 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -5241,39 +5093,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:51:48 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -5289,39 +5141,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 10:10:51 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>EPR Pay on Behalf charges for 2024 Amazon.co.uk sales</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -5340,39 +5192,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 12:21:34 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -5394,39 +5246,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:22:50 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -5448,39 +5300,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 16:23:48 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 4/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -5499,39 +5351,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 08:34:05 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5543,39 +5395,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:22:14 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5587,39 +5439,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:02:56 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 4/2026</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 4/2026 is now available in your Seller Central Account.
@@ -5631,39 +5483,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:29:17 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5675,39 +5527,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:25:39 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5719,39 +5571,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:10:57 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5763,39 +5615,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:09:44 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -5814,39 +5666,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:01:18 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -5865,39 +5717,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:25:07 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 4 2026</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 4 i rok 2026.
@@ -5909,39 +5761,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:24:35 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -5953,39 +5805,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:03:04 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -5997,39 +5849,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 20:51:50 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6041,39 +5893,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:44:14 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 4 2026</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 4 i rok 2026.
@@ -6085,39 +5937,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:35:59 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -6129,39 +5981,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:24:07 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6173,39 +6025,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:18:06 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6217,39 +6069,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:33:15 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6261,39 +6113,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:20:52 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6305,39 +6157,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:43:38 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -6349,39 +6201,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:17:48 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6393,39 +6245,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:52:53 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6437,40 +6289,40 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:40:42 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 4/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -6489,39 +6341,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:57:28 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6533,39 +6385,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:43:13 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6577,39 +6429,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:40:52 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6621,39 +6473,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:55:06 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6665,39 +6517,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:49:29 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6709,39 +6561,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:20:15 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -6762,39 +6614,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 15:00:42 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6809,39 +6661,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 14:24:59 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 4/2026 (Amazon.ae فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 4/2026)</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6860,39 +6712,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 05:32:15 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -6914,39 +6766,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:27:47 +0600</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Deals &lt;amazonreviewsdeals1@gmail.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Rating Deals</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>Not getting sales on Amazon? Even after doing everything right? Then this
 message is for you!
@@ -6972,40 +6824,40 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 03:15:52 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -7021,40 +6873,40 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:51 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -7070,39 +6922,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:45 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -7118,39 +6970,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 01:23:15 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -7166,39 +7018,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 15:09:15 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -7214,39 +7066,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:16:19 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -7260,39 +7112,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:33:13 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 04/2026</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -7310,40 +7162,40 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:34 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -7359,39 +7211,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:30 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -7407,39 +7259,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:21:43 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -7455,40 +7307,40 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:18:50 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -7504,39 +7356,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:55:17 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -7553,39 +7405,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:32:46 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -7614,39 +7466,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 15:08:42 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -7662,39 +7514,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:12:49 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -7708,39 +7560,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7755,39 +7607,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 10:18:53 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -7807,39 +7659,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 20:59:56 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para mayo</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para mayo
@@ -7868,40 +7720,40 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:37:52 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Il team di Gestione multicanale &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Aggiornamenti ai costi di Gestione multicanale in vigore dal 29
  maggio 2026</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
  Stiamo aggiornando le tariffe di Gestione multicanale per aiutarti a ridurre i costi e investire nella crescita della tua attività.
@@ -7914,39 +7766,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:30:37 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>The Multichannel Fulfillment team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>MCF fee updates effective May 29, 2026</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  We’re updating our Multichannel Fulfillment fees to help you reduce your costs so you can invest in growing your business.
@@ -7961,39 +7813,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:25:56 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>El Departamento de Logística Multicanal &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Actualización de las tarifas de Logística Multicanal en vigor a partir del 29 de mayo de 2026</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
  Vamos a actualizar nuestras tarifas de Logística Multicanal para ayudarte a reducir los costes y así puedas invertir en hacer crecer tu negocio.
@@ -8006,40 +7858,40 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:38:42 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Presenta documentos de cumplimiento normativo del producto para
  evitar que se retiren los listings</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta documentos de cumplimiento normativo del producto para evitar que se retiren los listings
@@ -8054,40 +7906,40 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:25:34 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Documenten over productconformiteit indienen om verwijdering van
  productvermeldingen te voorkomen</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
  Documenten over productconformiteit indienen om verwijdering van productvermeldingen te voorkomen
@@ -8101,39 +7953,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:06:50 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty
@@ -8147,39 +7999,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:58:32 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort
@@ -8194,39 +8046,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:54:06 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte
@@ -8240,39 +8092,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:50:08 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente
@@ -8287,39 +8139,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 15:58:40 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -8334,39 +8186,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Apr 2026 05:22:10 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -8385,39 +8237,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 11:10:42 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -8433,39 +8285,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 05:38:32 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -8486,340 +8338,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hola, Weihai EU:
- Algunos de tus listings están en riesgo de desactivación debido a que tus productos no cumplen los requisitos obligatorios. Revisa a continuación los detalles y siguientes pasos. Los listings afectados aparecen al final de este correo electrónico.
- ¿A qué se debe esto?
- Tomamos esta medida porque a estos productos les falta información de cumplimiento normativo obligatoria. Para más información sobre las leyes, normativas y políticas de Amazon aplicables, consulta Cumplimiento y seguridad de los productos .
- En la tabla que aparece al final de este correo electrónico se proporcionan los requisitos de cumplimiento normativo específicos del producto.
- ¿Cómo puedo reactivar mis listings?
- Para proporcionar la información de cumplimiento normativo obligatoria, ve a la página Estado de la cuenta y localiza las solicitudes de cumplimiento normativo del producto:
--
- Si dispones de la documentación obligatoria, sigue las instrucciones para presentar los documentos de cumplimiento normativo.
--
- Si crees que tus productos están exentos de estos requisitos, presenta documentación que demuestre por qué no están sujetos a estos requisitos de cumplimiento normativo.
- Para v</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 19:18:24 +0000</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t>Dien productveiligheidsdocumentatie in om de deactivering van de
- productvermelding te voorkomen</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hallo Weihai EU,
- Enkele van je productvermeldingen lopen het risico op deactivering omdat er verplichte nalevingsvereisten voor je producten ontbreken. Bekijk de gegevens en de stappen hieronder. De betreffende productvermeldingen worden aan het einde van deze e-mail weergegeven.
- Waarom gebeurt dit?
- We hebben deze actie ondernomen omdat voor deze producten verplichte nalevingsinformatie ontbreekt. Raadpleeg onze hulp-pagina Productveiligheid en -conformiteit voor informatie over de toepasselijke wet- en regelgeving en het Amazon-beleid.
- De tabel aan het einde van deze e-mail bevat productspecifieke nalevingsvereisten.
- Hoe activeer ik mijn productvermeldingen opnieuw?
- Als je de vereiste nalevingsgegevens wilt verstrekken, ga je naar de pagina Accountstatus en zoek je de aanvragen voor productconformiteit:
--
- Als je over de vereiste documentatie beschikt, volg je de instructies om je nalevingsdocumenten in te dienen.
--
- Als je van mening bent dat je producten zijn vrijgesteld van deze vereisten, dien dan documentatie in waaruit blijkt wat de reden is dat ze niet aan deze nalevingsvereisten zijn onderworpen.
- Raadpleeg voor stapsgewijze instructies onze hulp-pagina Documente</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 19:15:32 +0000</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>96
- Dzień dobry Weihai EU,
- niektóre z Twoich ofert są zagrożone dezaktywacją z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
- Dlaczego tak się stało?
- Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami .
- Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
- Jak mogę ponownie aktywować oferty?
- Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i znajdź żądania dotyczące zgodności produktu z wymogami:
--
- Jeśli dysponujesz wymaganymi dokumentami zgodności, postępuj zgodnie z instrukcjami, aby je przesłać.
--
- Jeśli uważasz, że Twoje produkty są zwolnione z wymogów dotyczących zgodności, prześlij d</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 19:12:50 +0000</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
-        </is>
-      </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hej Weihai EU!
- Vissa av dina produktposter riskerar att inaktiveras på grund av att det saknas obligatorisk information om överensstämmelse för produkterna. Granska informationen och följande steg nedan. De berörda produktposterna visas i slutet av det här e-postmeddelandet.
- Varför händer det här?
- Vi vidtar den här åtgärden eftersom det saknas obligatorisk information om överensstämmelse för de här produkterna. Läs vår hjälpsida för Produktsäkerhet och -överensstämmelse för information om tillämpliga lagar, förordningar och Amazons policyer.
- Tabellen i slutet av detta e-postmeddelande innehåller produktspecifika krav för överensstämmelse.
- Hur återaktiverar jag mina produktposter?
- Om du vill tillhandahålla den begärda överensstämmelseinformationen går du till sidan Kontostatus och letar upp begäranden om produktöverensstämmelse:
--
- Om du har den obligatoriska dokumentationen ska du skicka in dina överensstämmelsedokument enligt instruktionerna.
--
- Om du tror att dina produkter är undantagna från dessa krav skickar du in dokumentation som visar varför de inte omfattas av dessa överensstämmelsekrav.
- Du hittar stegvisa instruktioner på vår hjälpsida om Skicka in intyg om öve</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 19:12:30 +0000</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
- disattivazione dell'offerta</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>96
- Gentile Weihai EU,
- Alcune delle tue offerte sono a rischio di disattivazione perché i relativi prodotti non soddisfano i requisiti obbligatori sulla conformità. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
- Ciò a cosa è dovuto?
- Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili.
- La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
- Come faccio a riattivare le mie offerte?
- Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
--
- Se disponi della documentazione richiesta, segui le istruzioni per inviare i documenti di conformità.
--
- Se ritieni che i tuoi prodotti siano esenti da questi requisiti, invia la documentazione che dimostra il motivo per cui non sono soggetti a questi requisiti di conformità.
- Per istruzioni dettagliate, consulta l</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 19:09:22 +0000</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>96
- Bonjour Weihai EU,
- Certaines de vos mises en vente risquent d’être désactivées, car vos produits ne respectent pas les exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
- Pourquoi cela se produit-il ?
- Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables.
- Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
- Comment réactiver mes produits mis en vente ?
- Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
--
- Si vous disposez des documents requis, suivez les instructions pour soumettre vos documents de conformité.
--
- Si vous pensez que vos produits sont exemptés de ces exigences, soumettez des pièces justificatives prouvant les raisons pour lesquelles ils ne sont pas soumis à ces exigences de conformité.
- Pour des instru</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 04:51:55 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8843,39 +8394,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:58:34 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8896,39 +8447,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:50:26 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8951,39 +8502,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 04:43:42 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-21</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9007,39 +8558,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 03:34:49 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9062,39 +8613,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 04:46:00 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9118,39 +8669,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9174,39 +8725,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 03:35:07 +0000</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-07</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9227,39 +8778,39 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 11:38:29 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>You have until July 11 to verify FBA dimensions for fee calculation</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
  96
@@ -9268,39 +8819,39 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 00:16:37 +0000</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -9330,39 +8881,39 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 18:05:15 +0000</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
